--- a/analytikI/lety.xlsx
+++ b/analytikI/lety.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Lety" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -439,7 +439,7 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>typ_lietadla</t>
+          <t>typ lietadla</t>
         </is>
       </c>
     </row>
@@ -459,8 +459,10 @@
           <t>Berlín</t>
         </is>
       </c>
-      <c r="D2" t="n">
-        <v>150</v>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -484,8 +486,10 @@
           <t>Paríž</t>
         </is>
       </c>
-      <c r="D3" t="n">
-        <v>200</v>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -509,8 +513,10 @@
           <t>Rím</t>
         </is>
       </c>
-      <c r="D4" t="n">
-        <v>180</v>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -534,8 +540,10 @@
           <t>Madrid</t>
         </is>
       </c>
-      <c r="D5" t="n">
-        <v>220</v>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -559,8 +567,10 @@
           <t>Brusel</t>
         </is>
       </c>
-      <c r="D6" t="n">
-        <v>170</v>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>170</t>
+        </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>

--- a/analytikI/lety.xlsx
+++ b/analytikI/lety.xlsx
@@ -419,27 +419,27 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>cislo</t>
+          <t>Cislo</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>odlet</t>
+          <t>Odlet</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>ciel</t>
+          <t>Ciel</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>pocet_pasazierov</t>
+          <t>Pocet pasazierov</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>typ lietadla</t>
+          <t>Typ lietadla</t>
         </is>
       </c>
     </row>
@@ -459,10 +459,8 @@
           <t>Berlín</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
+      <c r="D2" t="n">
+        <v>150</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -486,10 +484,8 @@
           <t>Paríž</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
+      <c r="D3" t="n">
+        <v>200</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -513,10 +509,8 @@
           <t>Rím</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
+      <c r="D4" t="n">
+        <v>180</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -540,10 +534,8 @@
           <t>Madrid</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>220</t>
-        </is>
+      <c r="D5" t="n">
+        <v>220</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -567,10 +559,8 @@
           <t>Brusel</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>170</t>
-        </is>
+      <c r="D6" t="n">
+        <v>170</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
